--- a/ASTquizApp/qBanks/VOIP.xlsx
+++ b/ASTquizApp/qBanks/VOIP.xlsx
@@ -1,15 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programDo\vs\ASTquizApp\ASTquizApp\qBanks\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530718E8-E6ED-48F1-AC15-025D80A0DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$56</definedName>
@@ -19,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="206" count="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="206">
   <si>
     <t>VoIP</t>
   </si>
@@ -664,40 +668,37 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -741,12 +742,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -780,9 +777,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -792,47 +787,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -923,15 +884,53 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16" count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -969,7 +968,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1003,6 +1002,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1037,9 +1037,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1145,7 +1146,7 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
+            <a:lightRig rig="threePt" dir="t">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
@@ -1212,28 +1213,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P67"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O67"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" hidden="1" customWidth="1" width="18.855469" style="0"/>
-    <col min="2" max="2" hidden="1" customWidth="1" width="9.7109375" style="0"/>
-    <col min="3" max="3" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="4" max="4" hidden="1" customWidth="1" width="16.140625" style="0"/>
-    <col min="5" max="5" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="6" max="6" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="7" max="7" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="8" max="8" customWidth="1" bestFit="1" width="81.28516" style="0"/>
-    <col min="9" max="9" customWidth="1" width="15.855469" style="0"/>
-    <col min="10" max="10" customWidth="1" width="24.140625" style="0"/>
-    <col min="11" max="11" customWidth="1" width="24.570312" style="0"/>
-    <col min="12" max="12" customWidth="1" width="17.710938" style="0"/>
-    <col min="13" max="13" customWidth="1" width="10.425781" style="0"/>
-    <col min="14" max="14" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="15" max="15" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="81.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="10" max="10" width="24.140625" customWidth="1"/>
+    <col min="11" max="11" width="24.5703125" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" customWidth="1"/>
+    <col min="14" max="15" width="10" hidden="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:8" s="1" ht="18.75" customFormat="1">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="2" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>137</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>138</v>
       </c>
       <c r="C2" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>1</v>
@@ -1297,7 +1297,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>3</v>
@@ -1321,13 +1321,13 @@
         <v>8</v>
       </c>
       <c r="N2" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>137</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>138</v>
       </c>
       <c r="C3" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>3</v>
@@ -1368,13 +1368,13 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="4" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>137</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>138</v>
       </c>
       <c r="C4" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
@@ -1391,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>3</v>
@@ -1415,13 +1415,13 @@
         <v>10</v>
       </c>
       <c r="N4" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="5" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>137</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>138</v>
       </c>
       <c r="C5" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>1</v>
@@ -1438,7 +1438,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>21</v>
@@ -1458,13 +1458,13 @@
         <v>10</v>
       </c>
       <c r="N5" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="6" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>137</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>138</v>
       </c>
       <c r="C6" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>1</v>
@@ -1481,7 +1481,7 @@
         <v>15</v>
       </c>
       <c r="F6" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>3</v>
@@ -1505,13 +1505,13 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>137</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>138</v>
       </c>
       <c r="C7" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>3</v>
@@ -1552,13 +1552,13 @@
         <v>15</v>
       </c>
       <c r="N7" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>137</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>138</v>
       </c>
       <c r="C8" s="4">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>1</v>
@@ -1575,7 +1575,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>21</v>
@@ -1595,13 +1595,13 @@
         <v>10</v>
       </c>
       <c r="N8" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="9" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>137</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>138</v>
       </c>
       <c r="C9" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>1</v>
@@ -1618,7 +1618,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>3</v>
@@ -1642,13 +1642,13 @@
         <v>2</v>
       </c>
       <c r="N9" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>137</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>138</v>
       </c>
       <c r="C10" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>1</v>
@@ -1665,7 +1665,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>3</v>
@@ -1689,13 +1689,13 @@
         <v>15</v>
       </c>
       <c r="N10" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="8:8" s="3" ht="60.0" customFormat="1">
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>137</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>138</v>
       </c>
       <c r="C11" s="4">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>1</v>
@@ -1712,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="F11" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>21</v>
@@ -1732,13 +1732,13 @@
         <v>10</v>
       </c>
       <c r="N11" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="8:8" ht="60.0">
+    <row r="12" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>137</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>138</v>
       </c>
       <c r="C12" s="4">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>1</v>
@@ -1755,7 +1755,7 @@
         <v>15</v>
       </c>
       <c r="F12" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>3</v>
@@ -1779,13 +1779,13 @@
         <v>15</v>
       </c>
       <c r="N12" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O12" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="8:8" ht="60.0">
+    <row r="13" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>137</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>138</v>
       </c>
       <c r="C13" s="4">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>1</v>
@@ -1802,7 +1802,7 @@
         <v>10</v>
       </c>
       <c r="F13" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>3</v>
@@ -1826,13 +1826,13 @@
         <v>2</v>
       </c>
       <c r="N13" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O13" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="8:8" ht="60.0">
+    <row r="14" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>137</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>138</v>
       </c>
       <c r="C14" s="4">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>1</v>
@@ -1849,7 +1849,7 @@
         <v>15</v>
       </c>
       <c r="F14" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>3</v>
@@ -1873,13 +1873,13 @@
         <v>8</v>
       </c>
       <c r="N14" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O14" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="8:8" ht="60.0">
+    <row r="15" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>137</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>138</v>
       </c>
       <c r="C15" s="4">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>1</v>
@@ -1896,7 +1896,7 @@
         <v>8</v>
       </c>
       <c r="F15" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>3</v>
@@ -1920,13 +1920,13 @@
         <v>10</v>
       </c>
       <c r="N15" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O15" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="8:8" ht="60.0">
+    <row r="16" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>137</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>138</v>
       </c>
       <c r="C16" s="4">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>1</v>
@@ -1943,7 +1943,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>3</v>
@@ -1967,13 +1967,13 @@
         <v>2</v>
       </c>
       <c r="N16" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O16" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="8:8" ht="60.0">
+    <row r="17" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>137</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>138</v>
       </c>
       <c r="C17" s="4">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>1</v>
@@ -1990,7 +1990,7 @@
         <v>10</v>
       </c>
       <c r="F17" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>3</v>
@@ -2014,13 +2014,13 @@
         <v>8</v>
       </c>
       <c r="N17" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O17" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="8:8" ht="60.0">
+    <row r="18" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>137</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>138</v>
       </c>
       <c r="C18" s="4">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>1</v>
@@ -2037,7 +2037,7 @@
         <v>15</v>
       </c>
       <c r="F18" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>3</v>
@@ -2061,13 +2061,13 @@
         <v>8</v>
       </c>
       <c r="N18" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O18" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="8:8" ht="60.0">
+    <row r="19" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>137</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>138</v>
       </c>
       <c r="C19" s="4">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>1</v>
@@ -2084,7 +2084,7 @@
         <v>8</v>
       </c>
       <c r="F19" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>3</v>
@@ -2108,13 +2108,13 @@
         <v>8</v>
       </c>
       <c r="N19" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O19" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="8:8" ht="60.0">
+    <row r="20" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>137</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>138</v>
       </c>
       <c r="C20" s="4">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>84</v>
@@ -2131,7 +2131,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>3</v>
@@ -2155,13 +2155,13 @@
         <v>10</v>
       </c>
       <c r="N20" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O20" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="8:8" ht="60.0">
+    <row r="21" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>137</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>138</v>
       </c>
       <c r="C21" s="4">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>84</v>
@@ -2178,7 +2178,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>3</v>
@@ -2202,13 +2202,13 @@
         <v>2</v>
       </c>
       <c r="N21" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O21" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="8:8" ht="60.0">
+    <row r="22" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>137</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>138</v>
       </c>
       <c r="C22" s="4">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>84</v>
@@ -2225,7 +2225,7 @@
         <v>10</v>
       </c>
       <c r="F22" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>21</v>
@@ -2245,13 +2245,13 @@
         <v>10</v>
       </c>
       <c r="N22" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O22" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="8:8" ht="60.0">
+    <row r="23" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>137</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>138</v>
       </c>
       <c r="C23" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>84</v>
@@ -2268,7 +2268,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>21</v>
@@ -2288,13 +2288,13 @@
         <v>2</v>
       </c>
       <c r="N23" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O23" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="8:8" ht="60.0">
+    <row r="24" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>137</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>138</v>
       </c>
       <c r="C24" s="4">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>84</v>
@@ -2311,7 +2311,7 @@
         <v>8</v>
       </c>
       <c r="F24" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>21</v>
@@ -2331,13 +2331,13 @@
         <v>10</v>
       </c>
       <c r="N24" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O24" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="8:8" ht="60.0">
+    <row r="25" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>137</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>138</v>
       </c>
       <c r="C25" s="4">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>84</v>
@@ -2354,7 +2354,7 @@
         <v>15</v>
       </c>
       <c r="F25" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>21</v>
@@ -2374,13 +2374,13 @@
         <v>2</v>
       </c>
       <c r="N25" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O25" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="8:8" ht="60.0">
+    <row r="26" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>137</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>138</v>
       </c>
       <c r="C26" s="4">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>84</v>
@@ -2397,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>3</v>
@@ -2421,13 +2421,13 @@
         <v>15</v>
       </c>
       <c r="N26" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O26" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="8:8" ht="60.0">
+    <row r="27" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>137</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>138</v>
       </c>
       <c r="C27" s="4">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="D27" s="12" t="s">
         <v>84</v>
@@ -2444,7 +2444,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>21</v>
@@ -2464,13 +2464,13 @@
         <v>10</v>
       </c>
       <c r="N27" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O27" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="8:8" ht="60.0">
+    <row r="28" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>137</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>138</v>
       </c>
       <c r="C28" s="4">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="D28" s="12" t="s">
         <v>84</v>
@@ -2487,7 +2487,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>3</v>
@@ -2511,13 +2511,13 @@
         <v>2</v>
       </c>
       <c r="N28" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O28" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="8:8" ht="60.0">
+    <row r="29" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>137</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>138</v>
       </c>
       <c r="C29" s="4">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>84</v>
@@ -2534,7 +2534,7 @@
         <v>8</v>
       </c>
       <c r="F29" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>3</v>
@@ -2558,13 +2558,13 @@
         <v>10</v>
       </c>
       <c r="N29" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O29" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="8:8" ht="60.0">
+    <row r="30" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>137</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>138</v>
       </c>
       <c r="C30" s="4">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>84</v>
@@ -2581,7 +2581,7 @@
         <v>15</v>
       </c>
       <c r="F30" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>21</v>
@@ -2601,13 +2601,13 @@
         <v>10</v>
       </c>
       <c r="N30" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O30" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="8:8" ht="60.0">
+    <row r="31" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>137</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>138</v>
       </c>
       <c r="C31" s="4">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>84</v>
@@ -2624,7 +2624,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>21</v>
@@ -2644,13 +2644,13 @@
         <v>2</v>
       </c>
       <c r="N31" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="8:8" ht="60.0">
+    <row r="32" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>137</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>138</v>
       </c>
       <c r="C32" s="4">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>84</v>
@@ -2667,7 +2667,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>3</v>
@@ -2691,13 +2691,13 @@
         <v>15</v>
       </c>
       <c r="N32" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O32" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="8:8" ht="60.0">
+    <row r="33" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>137</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>138</v>
       </c>
       <c r="C33" s="4">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>84</v>
@@ -2714,7 +2714,7 @@
         <v>15</v>
       </c>
       <c r="F33" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>3</v>
@@ -2738,13 +2738,13 @@
         <v>8</v>
       </c>
       <c r="N33" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O33" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="8:8" ht="60.0">
+    <row r="34" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>137</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>138</v>
       </c>
       <c r="C34" s="4">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>84</v>
@@ -2761,7 +2761,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>3</v>
@@ -2785,13 +2785,13 @@
         <v>2</v>
       </c>
       <c r="N34" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O34" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="8:8" ht="60.0">
+    <row r="35" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>137</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>138</v>
       </c>
       <c r="C35" s="4">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="D35" s="12" t="s">
         <v>84</v>
@@ -2808,7 +2808,7 @@
         <v>8</v>
       </c>
       <c r="F35" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>21</v>
@@ -2828,13 +2828,13 @@
         <v>10</v>
       </c>
       <c r="N35" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O35" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="8:8" ht="60.0">
+    <row r="36" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>137</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>138</v>
       </c>
       <c r="C36" s="4">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>84</v>
@@ -2851,7 +2851,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>21</v>
@@ -2871,13 +2871,13 @@
         <v>2</v>
       </c>
       <c r="N36" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O36" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="8:8" ht="60.0">
+    <row r="37" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>137</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>138</v>
       </c>
       <c r="C37" s="4">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="D37" s="12" t="s">
         <v>84</v>
@@ -2894,7 +2894,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>3</v>
@@ -2918,13 +2918,13 @@
         <v>2</v>
       </c>
       <c r="N37" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O37" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="8:8" ht="60.0">
+    <row r="38" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>137</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>138</v>
       </c>
       <c r="C38" s="4">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>84</v>
@@ -2941,7 +2941,7 @@
         <v>8</v>
       </c>
       <c r="F38" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>3</v>
@@ -2965,13 +2965,13 @@
         <v>2</v>
       </c>
       <c r="N38" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O38" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="8:8" ht="60.0">
+    <row r="39" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>137</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>138</v>
       </c>
       <c r="C39" s="4">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="D39" s="12" t="s">
         <v>84</v>
@@ -2988,7 +2988,7 @@
         <v>15</v>
       </c>
       <c r="F39" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>3</v>
@@ -3012,13 +3012,13 @@
         <v>8</v>
       </c>
       <c r="N39" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O39" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="8:8" ht="60.0">
+    <row r="40" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>137</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>138</v>
       </c>
       <c r="C40" s="4">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="D40" s="12" t="s">
         <v>84</v>
@@ -3035,7 +3035,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>21</v>
@@ -3055,13 +3055,13 @@
         <v>10</v>
       </c>
       <c r="N40" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O40" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="8:8" ht="60.0">
+    <row r="41" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>137</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>138</v>
       </c>
       <c r="C41" s="4">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="D41" s="12" t="s">
         <v>84</v>
@@ -3078,7 +3078,7 @@
         <v>10</v>
       </c>
       <c r="F41" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>21</v>
@@ -3098,13 +3098,13 @@
         <v>2</v>
       </c>
       <c r="N41" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O41" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="42" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>137</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>138</v>
       </c>
       <c r="C42" s="4">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>139</v>
@@ -3121,7 +3121,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G42" s="15" t="s">
         <v>3</v>
@@ -3145,13 +3145,13 @@
         <v>10</v>
       </c>
       <c r="N42" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O42" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="43" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="43" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>137</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>138</v>
       </c>
       <c r="C43" s="4">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="D43" s="15" t="s">
         <v>139</v>
@@ -3168,7 +3168,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="15" t="s">
         <v>21</v>
@@ -3188,13 +3188,13 @@
         <v>10</v>
       </c>
       <c r="N43" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O43" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="44" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>137</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>138</v>
       </c>
       <c r="C44" s="4">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>139</v>
@@ -3211,7 +3211,7 @@
         <v>15</v>
       </c>
       <c r="F44" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="15" t="s">
         <v>3</v>
@@ -3235,13 +3235,13 @@
         <v>10</v>
       </c>
       <c r="N44" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O44" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="45" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="45" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>137</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>138</v>
       </c>
       <c r="C45" s="4">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="D45" s="15" t="s">
         <v>139</v>
@@ -3258,7 +3258,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="15" t="s">
         <v>3</v>
@@ -3282,13 +3282,13 @@
         <v>15</v>
       </c>
       <c r="N45" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O45" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="46" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="46" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>137</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>138</v>
       </c>
       <c r="C46" s="4">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>139</v>
@@ -3305,7 +3305,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G46" s="15" t="s">
         <v>3</v>
@@ -3329,13 +3329,13 @@
         <v>8</v>
       </c>
       <c r="N46" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O46" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="47" spans="8:8" s="14" ht="71.25" customFormat="1">
+    <row r="47" spans="1:15" s="14" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>137</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>138</v>
       </c>
       <c r="C47" s="4">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>161</v>
@@ -3352,7 +3352,7 @@
         <v>15</v>
       </c>
       <c r="F47" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="15" t="s">
         <v>3</v>
@@ -3376,13 +3376,13 @@
         <v>8</v>
       </c>
       <c r="N47" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O47" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="48" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>137</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>138</v>
       </c>
       <c r="C48" s="4">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="D48" s="15" t="s">
         <v>161</v>
@@ -3399,7 +3399,7 @@
         <v>8</v>
       </c>
       <c r="F48" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="15" t="s">
         <v>3</v>
@@ -3423,13 +3423,13 @@
         <v>8</v>
       </c>
       <c r="N48" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O48" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="49" spans="8:8" s="14" ht="85.5" customFormat="1">
+    <row r="49" spans="1:15" s="14" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>137</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>138</v>
       </c>
       <c r="C49" s="4">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="D49" s="15" t="s">
         <v>161</v>
@@ -3446,7 +3446,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G49" s="15" t="s">
         <v>3</v>
@@ -3470,13 +3470,13 @@
         <v>8</v>
       </c>
       <c r="N49" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O49" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="50" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>137</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>138</v>
       </c>
       <c r="C50" s="4">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>161</v>
@@ -3493,7 +3493,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="15" t="s">
         <v>21</v>
@@ -3513,13 +3513,13 @@
         <v>10</v>
       </c>
       <c r="N50" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O50" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="51" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="51" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>137</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>138</v>
       </c>
       <c r="C51" s="4">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="D51" s="15" t="s">
         <v>161</v>
@@ -3536,7 +3536,7 @@
         <v>15</v>
       </c>
       <c r="F51" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G51" s="15" t="s">
         <v>3</v>
@@ -3560,13 +3560,13 @@
         <v>8</v>
       </c>
       <c r="N51" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O51" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="52" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="52" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>137</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>138</v>
       </c>
       <c r="C52" s="4">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>180</v>
@@ -3583,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G52" s="15" t="s">
         <v>3</v>
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="N52" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O52" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="53" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="53" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>137</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>138</v>
       </c>
       <c r="C53" s="4">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="D53" s="15" t="s">
         <v>180</v>
@@ -3630,7 +3630,7 @@
         <v>8</v>
       </c>
       <c r="F53" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="15" t="s">
         <v>3</v>
@@ -3654,13 +3654,13 @@
         <v>15</v>
       </c>
       <c r="N53" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O53" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="54" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="54" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>137</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>138</v>
       </c>
       <c r="C54" s="4">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>180</v>
@@ -3677,7 +3677,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G54" s="15" t="s">
         <v>3</v>
@@ -3701,13 +3701,13 @@
         <v>2</v>
       </c>
       <c r="N54" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O54" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="55" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="55" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>137</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>138</v>
       </c>
       <c r="C55" s="4">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="D55" s="15" t="s">
         <v>196</v>
@@ -3724,7 +3724,7 @@
         <v>8</v>
       </c>
       <c r="F55" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G55" s="15" t="s">
         <v>3</v>
@@ -3748,13 +3748,13 @@
         <v>15</v>
       </c>
       <c r="N55" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O55" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="56" spans="8:8" s="14" ht="60.0" customFormat="1">
+    <row r="56" spans="1:15" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>137</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>138</v>
       </c>
       <c r="C56" s="4">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>196</v>
@@ -3771,7 +3771,7 @@
         <v>15</v>
       </c>
       <c r="F56" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G56" s="15" t="s">
         <v>3</v>
@@ -3795,13 +3795,13 @@
         <v>8</v>
       </c>
       <c r="N56" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O56" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="57" spans="8:8" ht="15.75">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -3818,7 +3818,7 @@
       <c r="N57" s="17"/>
       <c r="O57" s="17"/>
     </row>
-    <row r="58" spans="8:8" ht="15.75">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -3835,7 +3835,7 @@
       <c r="N58" s="17"/>
       <c r="O58" s="17"/>
     </row>
-    <row r="59" spans="8:8" ht="15.75">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -3852,7 +3852,7 @@
       <c r="N59" s="17"/>
       <c r="O59" s="17"/>
     </row>
-    <row r="60" spans="8:8" ht="15.75">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -3869,7 +3869,7 @@
       <c r="N60" s="17"/>
       <c r="O60" s="17"/>
     </row>
-    <row r="61" spans="8:8" ht="15.75">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="17"/>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
@@ -3886,7 +3886,7 @@
       <c r="N61" s="17"/>
       <c r="O61" s="17"/>
     </row>
-    <row r="62" spans="8:8" ht="15.75">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="17"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -3903,7 +3903,7 @@
       <c r="N62" s="17"/>
       <c r="O62" s="17"/>
     </row>
-    <row r="63" spans="8:8" ht="15.75">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="17"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -3920,7 +3920,7 @@
       <c r="N63" s="17"/>
       <c r="O63" s="17"/>
     </row>
-    <row r="64" spans="8:8" ht="15.75">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="17"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -3937,7 +3937,7 @@
       <c r="N64" s="17"/>
       <c r="O64" s="17"/>
     </row>
-    <row r="65" spans="8:8" ht="15.75">
+    <row r="65" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="19"/>
       <c r="B65" s="18"/>
       <c r="C65" s="17"/>
@@ -3954,7 +3954,7 @@
       <c r="N65" s="17"/>
       <c r="O65" s="17"/>
     </row>
-    <row r="66" spans="8:8" ht="15.75">
+    <row r="66" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="19"/>
       <c r="B66" s="18"/>
       <c r="C66" s="17"/>
@@ -3971,7 +3971,7 @@
       <c r="N66" s="17"/>
       <c r="O66" s="17"/>
     </row>
-    <row r="67" spans="8:8" ht="15.75">
+    <row r="67" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="19"/>
       <c r="B67" s="18"/>
       <c r="C67" s="17"/>
@@ -3990,41 +3990,23 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1">
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="9" dxfId="1"/>
-    <cfRule type="duplicateValues" priority="5" dxfId="2"/>
-    <cfRule type="duplicateValues" priority="6" dxfId="3"/>
-    <cfRule type="duplicateValues" priority="4" dxfId="4"/>
-    <cfRule type="duplicateValues" priority="3" dxfId="5"/>
-    <cfRule type="duplicateValues" priority="10" dxfId="6"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="7"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H11">
-    <cfRule type="duplicateValues" priority="12" dxfId="8"/>
-    <cfRule type="duplicateValues" priority="11" dxfId="9"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" priority="7" dxfId="10"/>
-    <cfRule type="duplicateValues" priority="8" dxfId="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>